--- a/СМИ_карточки_для_сайта.xlsx
+++ b/СМИ_карточки_для_сайта.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Россия" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="США и мир" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="СНГ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Россия" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="США и мир" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="СНГ" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Россия'!$A$1:$L$212</definedName>
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:M212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,11 @@
           <t>turnaround_days</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Logo URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -597,6 +602,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/srrb.ru</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -659,6 +669,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/apni.ru</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -721,6 +736,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tvkinoradio.ru</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -783,6 +803,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/politnavigator.net</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -845,6 +870,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bloknot.ru</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -907,6 +937,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/delovoymir.biz</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -969,6 +1004,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/business-magazine.online</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1031,6 +1071,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/garant.ru</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1093,6 +1138,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/prophotos.ru</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1155,6 +1205,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/peopletalk.ru</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1217,6 +1272,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/versia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1279,6 +1339,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/infox.ru</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1341,6 +1406,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/samag.ru</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1403,6 +1473,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/itweek.ru</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1465,6 +1540,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/1sept.ru</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1527,6 +1607,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/finversia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1589,6 +1674,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mir24.tv</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1651,6 +1741,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/lenta.ru</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1713,6 +1808,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/7days.ru</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1775,6 +1875,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/vokrug.tv</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1837,6 +1942,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fedpress.ru</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1899,6 +2009,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/securitylab.ru</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1961,6 +2076,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/osnmedia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2023,6 +2143,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/snob.ru</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2085,6 +2210,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/comnews.ru</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2147,6 +2277,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tproger.ru</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2209,6 +2344,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/cnews.ru</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2271,6 +2411,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/iz.ru</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2333,6 +2478,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sport-express.ru</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2395,6 +2545,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/newdaynews.ru</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2457,6 +2612,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gazetametro.ru</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2519,6 +2679,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/5-tv.ru</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2581,6 +2746,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dk.ru</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2643,6 +2813,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/strategyjournal.ru</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2705,6 +2880,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/retailer.ru</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2767,6 +2947,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mk.ru</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2829,6 +3014,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/aif.ru</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2891,6 +3081,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/vedomosti.ru</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2953,6 +3148,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ng.ru</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3015,6 +3215,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/business.ru</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3077,6 +3282,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kom-dir.ru</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3139,6 +3349,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/glavbukh.ru</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3201,6 +3416,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/26-2.ru</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3263,6 +3483,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/buhsoft.ru</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3325,6 +3550,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/pro-personal.ru</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3387,6 +3617,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kdelo.ru</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3449,6 +3684,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tass.ru</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3511,6 +3751,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gazeta.ru</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3573,6 +3818,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/vm.ru</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3635,6 +3885,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/news.ru</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3697,6 +3952,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/profile.ru</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3759,6 +4019,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/oilcapital.ru</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3821,6 +4086,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/business-gazeta.ru</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3883,6 +4153,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ko.ru</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3945,6 +4220,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dp.ru</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4007,6 +4287,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/popmech.ru</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4069,6 +4354,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/svpressa.ru</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4131,6 +4421,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ridus.ru</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4193,6 +4488,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dni.ru</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4255,6 +4555,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/utro.ru</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4317,6 +4622,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kleo.ru</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4379,6 +4689,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/newizv.ru</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4441,6 +4756,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/rosbalt.ru</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4503,6 +4823,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/monocle.ru</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4565,6 +4890,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/rg.ru</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4627,6 +4957,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/runews24.ru</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4689,6 +5024,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/angi.ru</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4751,6 +5091,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/naked-science.ru</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4813,6 +5158,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/globalcio.ru</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4875,6 +5225,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businesstory.ru</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4937,6 +5292,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ict-online.ru</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4999,6 +5359,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/logirus.ru</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5061,6 +5426,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/24gadget.ru</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5123,6 +5493,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/marieclaire.com</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5185,6 +5560,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/3dnews.ru</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5247,6 +5627,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/servernews.ru</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5309,6 +5694,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/new-retail.ru</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5371,6 +5761,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/nakanune.ru</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5433,6 +5828,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/telecomdaily.ru</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5495,6 +5895,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bigpicture.ru</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5557,6 +5962,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kommersant.ru</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5619,6 +6029,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/eadaily.com</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5681,6 +6096,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sostav.ru</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5743,6 +6163,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ura.news</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5805,6 +6230,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/seonews.ru</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5867,6 +6297,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/likeni.ru</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5929,6 +6364,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/life.ru</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5991,6 +6431,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sportmk.ru</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6053,6 +6498,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/omanhit.ru</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6115,6 +6565,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/avtovzglyad.ru</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6177,6 +6632,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ohotniki.ru</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6239,6 +6699,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mperspektiva.ru</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6301,6 +6766,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/beautyhack.ru</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6363,6 +6833,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sobaka.ru</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6425,6 +6900,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sobaka.ru</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6487,6 +6967,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sobaka.ru</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6549,6 +7034,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/forbes.ru</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6611,6 +7101,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/stroygaz.ru</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6673,6 +7168,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/regnum.ru</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6735,6 +7235,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/topcor.ru</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6797,6 +7302,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sfera.fm</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6859,6 +7369,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/brl.mk.ru</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6921,6 +7436,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/novate.ru</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6983,6 +7503,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/beautycarteblanche.ru</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -7045,6 +7570,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/vokrug.tv</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -7107,6 +7637,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/vokrugsveta.ru</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7169,6 +7704,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/oman.ru</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7231,6 +7771,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/day.ru</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7293,6 +7838,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thegirl.ru</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7355,6 +7905,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/starhit.ru</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7417,6 +7972,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/parents.ru</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7479,6 +8039,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mydecor.ru</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7541,6 +8106,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/doctorpiter.ru</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7603,6 +8173,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/the-day.ru</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7665,6 +8240,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/maximonline.ru</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7727,6 +8307,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/psychologies.ru</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7789,6 +8374,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fashiontime.ru</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7851,6 +8441,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/oane.ws</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7913,6 +8508,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/terrnews.com</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7975,6 +8575,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kadara.ru</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -8037,6 +8642,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/monavista.ru</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -8099,6 +8709,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/vestnik.net</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -8161,6 +8776,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/nvspost.ru</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -8223,6 +8843,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/spb.kp.ru</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -8285,6 +8910,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/belarus.kp.ru</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -8347,6 +8977,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/—</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8409,6 +9044,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/news-24.ru</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8471,6 +9111,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/smi24.news</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8533,6 +9178,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/obzor-gazet.ru</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8595,6 +9245,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/allmosnews.ru</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8657,6 +9312,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/promgoverment.ru</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8719,6 +9379,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/hotrs.su</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8781,6 +9446,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mirwiki.ru</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8843,6 +9513,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/news-bank.ru</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8905,6 +9580,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/frequentflyers.ru</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8967,6 +9647,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/adindex.ru</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -9029,6 +9714,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/artagmag.ru</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -9091,6 +9781,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sport24.ru</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -9153,6 +9848,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/prufy.ru</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -9215,6 +9915,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/schoolotzyv.ru</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -9277,6 +9982,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/moneytimes.ru</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -9339,6 +10049,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/english.pravda.ru</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -9401,6 +10116,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/medpulse.ru</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -9463,6 +10183,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/newsinfo.ru</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -9525,6 +10250,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/politonline.ru</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9587,6 +10317,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/greatlove.ru</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9649,6 +10384,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/yoki.ru</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9711,6 +10451,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ecosever.ru</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9773,6 +10518,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/nationaljournal.ru</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9835,6 +10585,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/rusday.com</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9897,6 +10652,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/electorat.info</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9959,6 +10719,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mostimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -10021,6 +10786,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/pora.ru</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -10083,6 +10853,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/glavtema.ru</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -10145,6 +10920,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/prbn.ru</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -10207,6 +10987,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bigness.ru</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -10269,6 +11054,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/militarytimes.ru</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -10331,6 +11121,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fizcultprivet.ru</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -10393,6 +11188,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/poplawok.ru</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -10455,6 +11255,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/autokolonka.ru</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -10517,6 +11322,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/repairshome.ru</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -10579,6 +11389,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dailyshow.ru</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -10641,6 +11456,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/missus.ru</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -10703,6 +11523,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bigcaucasus.com</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -10765,6 +11590,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/georgiatimes.info</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -10827,6 +11657,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/pravda.ru</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -10889,6 +11724,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/aviation21.ru</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10951,6 +11791,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/isguru.ru</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -11013,6 +11858,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/asninfo.ru</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -11075,6 +11925,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/78.ru</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -11137,6 +11992,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thevoicemag.ru</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -11199,6 +12059,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/moskvichmag.ru</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -11261,6 +12126,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/rbc.ru</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -11323,6 +12193,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/moslenta.ru</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -11385,6 +12260,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kapital.kz</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -11447,6 +12327,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/lsm.kz</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -11509,6 +12394,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/newsmaker.md</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -11571,6 +12461,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/akipress.org</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -11633,6 +12528,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/24.kg</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -11695,6 +12595,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/noi.md</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -11757,6 +12662,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/uzdaily.uz</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -11819,6 +12729,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/inform.kz</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -11881,6 +12796,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/remedium.ru</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -11943,6 +12863,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/medvestnik.ru</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -12005,6 +12930,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/incrussia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -12067,6 +12997,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/apptractor.ru</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -12129,6 +13064,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/investfuture.ru</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -12191,6 +13131,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/onliner.by</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -12253,6 +13198,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bits.media</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -12315,6 +13265,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/telegraf.news</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -12377,6 +13332,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/liter.kz</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -12439,6 +13399,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/orda.kz</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -12501,6 +13466,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dcjournal.ru</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -12563,6 +13533,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/telecombloger.ru</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -12625,6 +13600,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/urbc.ru</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -12687,6 +13667,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/haqqin.az</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -12749,6 +13734,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mosregion.info</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -12811,6 +13801,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sila-rf.ru</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -12873,6 +13868,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sibmedia.ru</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -12935,6 +13935,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ladys.media</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -12997,6 +14002,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/socialinform.ru</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -13059,6 +14069,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/myeconomy.ru</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -13121,6 +14136,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ecopravda.ru</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -13183,6 +14203,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/medzdrav.info</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -13245,6 +14270,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/today.ua</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -13307,6 +14337,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/beautyhunter.ru</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -13369,6 +14404,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/informator.ua</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -13431,6 +14471,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/itechua.com</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -13493,6 +14538,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mignews.ua</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -13555,6 +14605,11 @@
           <t>от 3–7 рабочих дней</t>
         </is>
       </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/it-world.ru</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -13616,6 +14671,11 @@
       <c r="L212" s="2" t="inlineStr">
         <is>
           <t>от 3–7 рабочих дней</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gazeta.ua</t>
         </is>
       </c>
     </row>
@@ -13631,7 +14691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M354"/>
+  <dimension ref="A1:N354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13715,6 +14775,11 @@
           <t>turnaround_days</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Logo URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -13782,6 +14847,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/homebusinessmag.com</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -13849,6 +14919,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/miamiherald.com</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -13916,6 +14991,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kansascity.com</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -13983,6 +15063,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techtimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -14050,6 +15135,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/brainzmagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -14117,6 +15207,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/latinpost.com</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -14184,6 +15279,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/jpost.com</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -14251,6 +15351,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thewestnews.com</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -14318,6 +15423,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/vinnews.com</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -14385,6 +15495,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fxstreet.com</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -14452,6 +15567,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/inc.com</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -14519,6 +15639,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/computing.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -14586,6 +15711,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/crn.com</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -14653,6 +15783,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/intlbm.com</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -14720,6 +15855,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/adexchanger.com</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -14787,6 +15927,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thedrum.com</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -14854,6 +15999,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/globalbankingandfinance.com</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -14921,6 +16071,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/financedigest.com</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -14988,6 +16143,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fastcompany.com</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -15055,6 +16215,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/technologymagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -15122,6 +16287,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/aimagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -15189,6 +16359,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businesschief.eu</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -15256,6 +16431,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/housingwire.com</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -15323,6 +16503,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/paymentscardsandmobile.com</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -15390,6 +16575,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/digitalconnectmag.com</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -15457,6 +16647,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/healthcarebusinesstoday.com</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -15524,6 +16719,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/digiday.com</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -15591,6 +16791,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/aitimejournal.com</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -15658,6 +16863,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/geekextreme.com</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -15725,6 +16935,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/coingape.com</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -15792,6 +17007,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/arabianbusiness.com</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -15859,6 +17079,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businesstechnet.com</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -15926,6 +17151,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techstacy.com</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -15993,6 +17223,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/europeanbusinessreview.com</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -16060,6 +17295,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/educationtechnologyinsights.com</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -16127,6 +17367,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/digitaljournal.com</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -16194,6 +17439,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ealthybyte.com</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -16261,6 +17511,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techinasia.com</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -16328,6 +17583,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/siliconcanals.com</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -16395,6 +17655,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bizfortune.com</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -16462,6 +17727,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ciobulletin.com</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -16529,6 +17799,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/abcmoney.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -16596,6 +17871,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ceo-review.com</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -16663,6 +17943,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/corporatevision-news.com</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -16730,6 +18015,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/startupsmagazine.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -16797,6 +18087,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/lux-life.digital</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -16864,6 +18159,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/build-review.com</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -16931,6 +18231,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/smenews.digital</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -16998,6 +18303,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ghpnews.digital</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -17065,6 +18375,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/acquisition-international.com</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -17132,6 +18447,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ealthandfinance.digital</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -17199,6 +18519,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/eubusinessnews.com</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -17266,6 +18591,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/meamarkets.digital</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -17333,6 +18663,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/apacinsider.digital</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -17400,6 +18735,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/coventryobserver.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -17467,6 +18807,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bromsgrovestandard.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -17534,6 +18879,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/droitwichstandard.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -17601,6 +18951,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/eveshamobserver.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -17668,6 +19023,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kidderminsterstandard.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -17735,6 +19095,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/leamingtonobserver.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -17802,6 +19167,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/malvernobserver.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -17869,6 +19239,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/redditchstandard.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -17936,6 +19311,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/rugbyobserver.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -18003,6 +19383,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/solihullobserver.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -18070,6 +19455,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/stratfordobserver.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -18137,6 +19527,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/orcesterobserver.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -18204,6 +19599,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/richmond.com</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -18271,6 +19671,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fredericksburg.com</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -18338,6 +19743,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/roanoke.com</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -18405,6 +19815,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/newsadvance.com</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -18472,6 +19887,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dailyprogress.com</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -18539,6 +19959,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/heraldcourier.com</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -18606,6 +20031,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/martinsvillebulletin.com</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -18673,6 +20103,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/newsvirginian.com</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -18740,6 +20175,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thefranklinnewspost.com</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -18807,6 +20247,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/godanriver.com</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -18874,6 +20319,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/starexponent.com</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -18941,6 +20391,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/smithmountainlake.com</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -19008,6 +20463,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/swvatoday.com</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -19075,6 +20535,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/naludamagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -19142,6 +20607,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tech-critter.com</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -19209,6 +20679,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/nasilemaktech.com</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -19276,6 +20751,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/myeverydaytech.com</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -19343,6 +20823,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businessfostermagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -19410,6 +20895,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/business-money.com</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -19477,6 +20967,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businesscloud.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -19544,6 +21039,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gritdaily.com</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -19611,6 +21111,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thesiliconreview.com</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -19678,6 +21183,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thestreet.com</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -19745,6 +21255,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thedefiant.io</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -19812,6 +21327,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/smartechdaily.com</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -19879,6 +21399,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/meditechtoday.com</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -19946,6 +21471,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/financialtechtimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -20013,6 +21543,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/blocktelegraph.io</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -20080,6 +21615,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/transittomorrow.com</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -20147,6 +21687,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/highnetworthmag.com</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -20214,6 +21759,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/pharmatechnews.com</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -20281,6 +21831,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/luxurylamag.com</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -20348,6 +21903,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/luxurymiamimag.com</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -20415,6 +21975,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/lawnewsday.com</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -20482,6 +22047,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gametechdaily.com</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -20549,6 +22119,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ealthtechdaily.com</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -20616,6 +22191,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sportstechtoday.com</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -20683,6 +22263,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/meditechwire.com</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -20750,6 +22335,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/coinreviewnews.com</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -20817,6 +22407,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/innotechtoday.com</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -20884,6 +22479,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/csq.com</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -20951,6 +22551,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techfundingnews.com</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -21018,6 +22623,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/millennialmagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -21085,6 +22695,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/deccanherald.com</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -21152,6 +22767,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/amazingarchitecture.com</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -21219,6 +22839,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/healthworkscollective.com</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -21286,6 +22911,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/goodmenproject.com</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -21353,6 +22983,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gilmorehealth.com</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -21420,6 +23055,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/papermag.com</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -21487,6 +23127,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bust.com</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -21554,6 +23199,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/villagevoice.com</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -21621,6 +23271,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/irvineweekly.com</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -21688,6 +23343,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/marinatimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -21755,6 +23415,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thecharlotteweekly.com</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -21822,6 +23487,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/theleadernews.com</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -21889,6 +23559,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fortbendstar.com</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -21956,6 +23631,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/lakerlutznews.com</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -22023,6 +23703,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/laweekly.com</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -22090,6 +23775,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ocweekly.com</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -22157,6 +23847,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/inbuzzer.com</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -22224,6 +23919,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businessmole.com</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -22291,6 +23991,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/instrumentalfx.co</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -22358,6 +24063,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fadmagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -22425,6 +24135,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/eraveyou.com</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -22492,6 +24207,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sportsgossip.com</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -22559,6 +24279,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sportsmedia101.com</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -22626,6 +24351,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bostonsportsextra.com</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -22693,6 +24423,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fangsbites.com</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -22760,6 +24495,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/alltechmagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -22827,6 +24567,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/architectureartdesigns.com</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -22894,6 +24639,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ceotodaymagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -22961,6 +24711,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/insidermonkey.com</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -23028,6 +24783,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/securityonline.info</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -23095,6 +24855,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/securityexpress.info</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -23162,6 +24927,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/meterpreter.org</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -23229,6 +24999,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techiexpert.com</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -23296,6 +25071,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/luxuryhousingtrends.com</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -23363,6 +25143,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/iplocation.net</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -23430,6 +25215,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/opsmatters.com</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -23497,6 +25287,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businesshonor.com</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -23564,6 +25359,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/highways.today</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -23631,6 +25431,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/hometownstation.com</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -23698,6 +25503,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/latintimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -23765,6 +25575,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techloy.com</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -23832,6 +25647,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/americancraftbeer.com</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -23899,6 +25719,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/beerconnoisseur.com</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -23966,6 +25791,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/porchdrinking.com</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -24033,6 +25863,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mantelligence.com</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -24100,6 +25935,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/brulosophy.com</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -24167,6 +26007,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ashingtonbeerblog.com</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -24234,6 +26079,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/breweriesinpa.com</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -24301,6 +26151,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sandiegobeer.news</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -24368,6 +26223,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/livemusicblog.com</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -24435,6 +26295,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/mybeerbuzz.com</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -24502,6 +26367,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/highways.today</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -24569,6 +26439,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/luxuryhousingtrends.com</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -24636,6 +26511,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/timesla.com</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -24703,6 +26583,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gearrice.com</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -24770,6 +26655,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/inkl.com</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -24837,6 +26727,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/nyweekly.com</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -24904,6 +26799,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/artistweekly.com</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -24971,6 +26871,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ceoweekly.com</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -25038,6 +26943,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/atlwire.com</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -25105,6 +27015,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thechicagojournal.com</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -25172,6 +27087,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/emonthlynews.com</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -25239,6 +27159,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/lawire.com</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -25306,6 +27231,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/beautyscene.net</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -25373,6 +27303,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/londonlovesproperty.com</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -25440,6 +27375,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/londonlovestech.com</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -25507,6 +27447,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/nimvo.com</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -25574,6 +27519,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/chaospin.com</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -25641,6 +27591,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/malemodelscene.net</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -25708,6 +27663,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thebusinesswomanmedia.com</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -25775,6 +27735,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techbullion.com</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -25842,6 +27807,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fashionuer.com</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -25909,6 +27879,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/moneyinc.com</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -25976,6 +27951,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/londonlovesbusiness.com</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -26043,6 +28023,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bmmagazine.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -26110,6 +28095,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/designscene.net</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -26177,6 +28167,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fashionuer.com</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -26244,6 +28239,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/entrepreneurhandbook.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -26311,6 +28311,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/notorious-mag.com</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -26378,6 +28383,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thelondoneconomic.com</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -26445,6 +28455,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techstartups.com</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -26512,6 +28527,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/swaggermagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -26579,6 +28599,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/aijourn.com</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -26646,6 +28671,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/financefeeds.com</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -26713,6 +28743,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sciencetimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -26780,6 +28815,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/itechpost.com</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -26847,6 +28887,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/plainenglish.io</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -26914,6 +28959,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techround.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -26981,6 +29031,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/eureporter.co</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -27048,6 +29103,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dataconomy.com</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -27115,6 +29175,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ceoworld.biz</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -27182,6 +29247,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/allwomenstalk.com</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -27249,6 +29319,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ceoworld.biz</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -27316,6 +29391,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/u.today</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -27383,6 +29463,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/esternjournal.com</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -27450,6 +29535,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techworm.net</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -27517,6 +29607,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ibtimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -27584,6 +29679,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/theubj.com</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -27651,6 +29751,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/archiscene.net</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -27718,6 +29823,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/largest.org</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -27785,6 +29895,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dailycivil.com</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -27852,6 +29967,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tidtiltech.dk</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -27919,6 +30039,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/asianatimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -27986,6 +30111,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/musicraiser.net</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -28053,6 +30183,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/utilizewindows.com</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -28120,6 +30255,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thetvjunkies.com</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -28187,6 +30327,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tu.tv</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -28254,6 +30399,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/networthrant.com</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -28321,6 +30471,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/jewelbeat.com</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -28388,6 +30543,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/desksgram.net</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -28455,6 +30615,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/vxchnge.com</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -28522,6 +30687,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/liberalco.org</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -28589,6 +30759,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kiwibox.com</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -28656,6 +30831,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ebsta.me</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -28723,6 +30903,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techktimes.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -28790,6 +30975,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/koreaittimes.com</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -28857,6 +31047,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/breakingac.com</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -28924,6 +31119,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/maryberryrecipes.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -28991,6 +31191,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/londontime.co</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -29058,6 +31263,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/theluxurylifestylemagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -29125,6 +31335,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/luxurylifestylemag.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -29192,6 +31407,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/luxurialifestyle.com</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -29259,6 +31479,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/spacedaily.com</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -29326,6 +31551,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/racinecountyeye.com</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -29393,6 +31623,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/timesofisrael.com</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -29460,6 +31695,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/hardreset.info</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -29527,6 +31767,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/imei.info</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -29594,6 +31839,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/applesn.info</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -29661,6 +31911,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dataconomy.com</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -29728,6 +31983,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/radaronline.com</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -29795,6 +32055,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/okmagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -29862,6 +32127,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/onderwall.com</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -29929,6 +32199,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/knewz.com</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -29996,6 +32271,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/frontpagedetectives.com</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -30063,6 +32343,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/omensgolfjournal.com</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -30130,6 +32415,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/morninghoney.com</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -30197,6 +32487,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/dailycoin.com</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -30264,6 +32559,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bestforandroid.com</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -30331,6 +32631,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/esthawaiitoday.com</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -30398,6 +32703,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/midweek.com</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -30465,6 +32775,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/hawaiitribune-herald.com</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -30532,6 +32847,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/thegardenisland.com</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -30599,6 +32919,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/staradvertiser.com</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -30666,6 +32991,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ustimesnow.com</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -30733,6 +33063,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/homecrux.com</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -30800,6 +33135,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/modelifestylemagazine.com</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -30867,6 +33207,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/aiworldtoday.net</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -30934,6 +33279,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/digitalconvey.com</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -31001,6 +33351,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/trillmag.com</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -31068,6 +33423,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businessoutstanders.com</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -31135,6 +33495,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/metapress.com</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -31202,6 +33567,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/geeky-gadgets.com</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -31269,6 +33639,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gizchina.com</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -31336,6 +33711,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/coinprwire.com</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -31403,6 +33783,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/psbios.me</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -31470,6 +33855,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/timebulletin.com</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -31537,6 +33927,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/cyberpress.org</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -31604,6 +33999,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gbhackers.com</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -31671,6 +34071,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/cybersecuritynews.com</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -31738,6 +34143,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/analyticsinsight.net</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -31805,6 +34215,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/secureblitz.com</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -31872,6 +34287,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techdee.com</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -31939,6 +34359,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/talkandroid.com</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -32006,6 +34431,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/technology.org</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -32073,6 +34503,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/kalilinuxtutorials.com</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -32140,6 +34575,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/startup.info</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -32207,6 +34647,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fontsarena.com</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -32274,6 +34719,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/applegazette.com</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -32341,6 +34791,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bonjouridee.com</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -32408,6 +34863,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/hardwaresecrets.com</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -32475,6 +34935,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/fontmirror.com</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -32542,6 +35007,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/technochops.com</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -32609,6 +35079,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/socialnewsdaily.com</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -32676,6 +35151,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/cssbasics.com</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -32743,6 +35223,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tubetorial.com</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -32810,6 +35295,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/apps.uk</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -32877,6 +35367,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/paktales.com</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -32944,6 +35439,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/только</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -33011,6 +35511,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techdee.com</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -33078,6 +35583,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/technoroll.org</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -33145,6 +35655,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techstrange.com</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -33212,6 +35727,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techrado.com</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -33279,6 +35799,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/travellingforbusiness.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -33346,6 +35871,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/evpowered.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -33413,6 +35943,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/electrichome.uk</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -33480,6 +36015,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/propertyportfolioinvestor.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -33547,6 +36087,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techzeel.net</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -33614,6 +36159,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/learningtoday.net</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -33681,6 +36231,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/allinsider.net</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -33748,6 +36303,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sportzbuzz.net</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -33815,6 +36375,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/nextluxury.com</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -33882,6 +36447,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/stepbystepbusiness.com</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -33949,6 +36519,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/jt.org</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -34016,6 +36591,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/blueandgreentomorrow.com</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -34083,6 +36663,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techspotty.com</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -34150,6 +36735,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/aboutchromebooks.com</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -34217,6 +36807,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/digitaledge.org</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -34284,6 +36879,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/connectioncafe.com</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -34351,6 +36951,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tabletmonkeys.com</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -34418,6 +37023,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/quantumrun.com</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -34485,6 +37095,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/gadgetfreeks.com</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -34552,6 +37167,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/hatsontech.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -34619,6 +37239,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/voddler.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -34686,6 +37311,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/citybiz.co</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -34753,6 +37383,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/insiderpaper.com</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -34820,6 +37455,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/onlinebizbooster.net</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -34887,6 +37527,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businessandpower.com</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -34954,6 +37599,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/solidsmack.com</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -35021,6 +37671,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/jguru.com</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -35088,6 +37743,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/alltechbuzz.net</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -35155,6 +37815,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/baycitizen.org</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -35222,6 +37887,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/silicon</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -35289,6 +37959,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/triphippies.com</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -35356,6 +38031,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/learningtoday.net</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -35423,6 +38103,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ecommercefastlane.com</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -35490,6 +38175,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/netizensreport.com</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -35557,6 +38247,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/startup</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -35624,6 +38319,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/guruhitech.com</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -35691,6 +38391,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/britishwire.com</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -35758,6 +38463,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/investing.com</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -35825,6 +38535,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/the-tech-trend.com</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -35892,6 +38607,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/arrington-worldwide.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -35959,6 +38679,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/archeyes.com</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -36026,6 +38751,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/sportswane.com</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -36093,6 +38823,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/techwalls.com</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -36160,6 +38895,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/lawbhoomi.com</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -36227,6 +38967,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/businessnewsthisweek.com</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -36294,6 +39039,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/guardian.ng</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -36361,6 +39111,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/londondaily.news</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -36428,6 +39183,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/london-post.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -36495,6 +39255,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/omenontopp.com</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -36562,6 +39327,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/impactwealth.org</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -36629,6 +39399,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/africa.businessinsider.com</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -36696,6 +39471,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/measurescopez.com</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -36763,6 +39543,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ukbusinesstimes.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -36830,6 +39615,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/londoninsider.co.uk</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -36897,6 +39687,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/ibusiness.news</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -36964,6 +39759,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/theluxauthority.com</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -37031,6 +39831,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/congress.net</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -37098,6 +39903,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/bitzuma.com</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -37165,6 +39975,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/asiapresswire.com</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -37232,6 +40047,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/grazia.si</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -37299,6 +40119,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/luxuo.com</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -37364,6 +40189,11 @@
       <c r="M354" s="2" t="inlineStr">
         <is>
           <t>3–7 business days</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/glamour.bg</t>
         </is>
       </c>
     </row>
@@ -37379,7 +40209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -37457,6 +40287,11 @@
           <t>turnaround_days</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Logo URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -37519,6 +40354,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/digitalbusiness.kz</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -37581,6 +40421,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/zakon.kz</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -37643,6 +40488,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/informburo.kz</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -37705,6 +40555,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/rasdaily.kz</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -37767,6 +40622,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/caravan.kz</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -37829,6 +40689,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/tengrinews.kz</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -37891,6 +40756,11 @@
           <t>3–7 business days</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/centralmedia24.kz</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -37951,6 +40821,11 @@
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>3–7 business days</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://logo.clearbit.com/orda.kz</t>
         </is>
       </c>
     </row>
